--- a/public/exports-from-60-with-coowners/29189560.xlsx
+++ b/public/exports-from-60-with-coowners/29189560.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200027989</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189560.xlsx
+++ b/public/exports-from-60-with-coowners/29189560.xlsx
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027989</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251069</t>
+          <t xml:space="preserve">311251072</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189560.xlsx
+++ b/public/exports-from-60-with-coowners/29189560.xlsx
@@ -23989,7 +23989,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24364,7 +24364,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251072</t>
+          <t xml:space="preserve">311251069</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
